--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K646"/>
+  <dimension ref="A1:K648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25624,6 +25624,84 @@
         <v>324.99</v>
       </c>
       <c r="K646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>334.02</v>
+      </c>
+      <c r="C647" t="n">
+        <v>330.53</v>
+      </c>
+      <c r="D647" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="E647" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="F647" t="n">
+        <v>344.66</v>
+      </c>
+      <c r="G647" t="n">
+        <v>341.23</v>
+      </c>
+      <c r="H647" t="n">
+        <v>343.33</v>
+      </c>
+      <c r="I647" t="n">
+        <v>332.57</v>
+      </c>
+      <c r="J647" t="n">
+        <v>323.17</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="C648" t="n">
+        <v>331.35</v>
+      </c>
+      <c r="D648" t="n">
+        <v>337.04</v>
+      </c>
+      <c r="E648" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="F648" t="n">
+        <v>345.05</v>
+      </c>
+      <c r="G648" t="n">
+        <v>341.53</v>
+      </c>
+      <c r="H648" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="I648" t="n">
+        <v>332.07</v>
+      </c>
+      <c r="J648" t="n">
+        <v>324.16</v>
+      </c>
+      <c r="K648" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25640,7 +25718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B662"/>
+  <dimension ref="A1:B664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32263,6 +32341,26 @@
       </c>
       <c r="B662" t="n">
         <v>-0.43</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>
@@ -32431,28 +32529,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3643651554439843</v>
+        <v>-0.3689841835084145</v>
       </c>
       <c r="J2" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K2" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3243501637740049</v>
+        <v>0.3288814303209497</v>
       </c>
       <c r="M2" t="n">
-        <v>3.002522769168445</v>
+        <v>3.013348715278887</v>
       </c>
       <c r="N2" t="n">
-        <v>15.34873958530226</v>
+        <v>15.47637673249073</v>
       </c>
       <c r="O2" t="n">
-        <v>3.917746748489782</v>
+        <v>3.93400263503861</v>
       </c>
       <c r="P2" t="n">
-        <v>351.6612945747274</v>
+        <v>351.7089531184953</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32513,28 +32611,28 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.38942213075979</v>
+        <v>-0.3945636844271005</v>
       </c>
       <c r="J3" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K3" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3751298276897557</v>
+        <v>0.3792740685215581</v>
       </c>
       <c r="M3" t="n">
-        <v>2.867255467879221</v>
+        <v>2.885476034868782</v>
       </c>
       <c r="N3" t="n">
-        <v>14.01977168459307</v>
+        <v>14.19302108010601</v>
       </c>
       <c r="O3" t="n">
-        <v>3.744298557085568</v>
+        <v>3.767362615956421</v>
       </c>
       <c r="P3" t="n">
-        <v>349.6135237901592</v>
+        <v>349.6665737352562</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32595,28 +32693,28 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.459838618448468</v>
+        <v>-0.4638527266723972</v>
       </c>
       <c r="J4" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K4" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3708780487323043</v>
+        <v>0.3749786709014623</v>
       </c>
       <c r="M4" t="n">
-        <v>3.503918887241617</v>
+        <v>3.518775005678276</v>
       </c>
       <c r="N4" t="n">
-        <v>19.90701205729772</v>
+        <v>19.97755748456483</v>
       </c>
       <c r="O4" t="n">
-        <v>4.46172747456607</v>
+        <v>4.469626101204085</v>
       </c>
       <c r="P4" t="n">
-        <v>355.3508177853449</v>
+        <v>355.3922348596092</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32677,28 +32775,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2264197843058074</v>
+        <v>-0.2296774378486987</v>
       </c>
       <c r="J5" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K5" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1786710390946173</v>
+        <v>0.1829200907073931</v>
       </c>
       <c r="M5" t="n">
-        <v>2.715887442559944</v>
+        <v>2.725452338816088</v>
       </c>
       <c r="N5" t="n">
-        <v>13.07926096212207</v>
+        <v>13.12603875241247</v>
       </c>
       <c r="O5" t="n">
-        <v>3.616526090341678</v>
+        <v>3.622987545163862</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0628204422222</v>
+        <v>359.0964324723908</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -32759,28 +32857,28 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1784509178144867</v>
+        <v>-0.1810813687863652</v>
       </c>
       <c r="J6" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K6" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1459584564852091</v>
+        <v>0.1498108864318656</v>
       </c>
       <c r="M6" t="n">
-        <v>2.464336850601964</v>
+        <v>2.47042461442394</v>
       </c>
       <c r="N6" t="n">
-        <v>10.34138706307035</v>
+        <v>10.3660569819136</v>
       </c>
       <c r="O6" t="n">
-        <v>3.215802708978017</v>
+        <v>3.219636156759579</v>
       </c>
       <c r="P6" t="n">
-        <v>353.8620207368913</v>
+        <v>353.8891614265057</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32841,28 +32939,28 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2134638013815186</v>
+        <v>-0.214526911125019</v>
       </c>
       <c r="J7" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K7" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1399403146521692</v>
+        <v>0.1418904447520508</v>
       </c>
       <c r="M7" t="n">
-        <v>3.041313614143964</v>
+        <v>3.038248422437315</v>
       </c>
       <c r="N7" t="n">
-        <v>15.62058377318475</v>
+        <v>15.58167249619206</v>
       </c>
       <c r="O7" t="n">
-        <v>3.952288422317474</v>
+        <v>3.947362726706536</v>
       </c>
       <c r="P7" t="n">
-        <v>348.7554982080154</v>
+        <v>348.7664267017032</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32923,28 +33021,28 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1969902183326603</v>
+        <v>-0.1970245080971083</v>
       </c>
       <c r="J8" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K8" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1001999387640303</v>
+        <v>0.100842677310843</v>
       </c>
       <c r="M8" t="n">
-        <v>3.374950358674054</v>
+        <v>3.365450135002445</v>
       </c>
       <c r="N8" t="n">
-        <v>19.43707554479936</v>
+        <v>19.37727695558047</v>
       </c>
       <c r="O8" t="n">
-        <v>4.408749884581724</v>
+        <v>4.401962852589794</v>
       </c>
       <c r="P8" t="n">
-        <v>348.8874875462419</v>
+        <v>348.8878399235982</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33005,28 +33103,28 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2770904400763445</v>
+        <v>-0.2791184371327838</v>
       </c>
       <c r="J9" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K9" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09212421853800967</v>
+        <v>0.09385892117876005</v>
       </c>
       <c r="M9" t="n">
-        <v>5.050700041562991</v>
+        <v>5.047056967804384</v>
       </c>
       <c r="N9" t="n">
-        <v>41.99399436923151</v>
+        <v>41.89779803996286</v>
       </c>
       <c r="O9" t="n">
-        <v>6.480277337370023</v>
+        <v>6.472850843327294</v>
       </c>
       <c r="P9" t="n">
-        <v>342.9411377390263</v>
+        <v>342.9620625320785</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33087,28 +33185,28 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2042791940916419</v>
+        <v>-0.211438987306568</v>
       </c>
       <c r="J10" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K10" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04141074905240516</v>
+        <v>0.04419004971042317</v>
       </c>
       <c r="M10" t="n">
-        <v>5.927954132604001</v>
+        <v>5.947838541438898</v>
       </c>
       <c r="N10" t="n">
-        <v>53.61165657715326</v>
+        <v>53.86554843315695</v>
       </c>
       <c r="O10" t="n">
-        <v>7.32199812736614</v>
+        <v>7.33931525642256</v>
       </c>
       <c r="P10" t="n">
-        <v>340.7473003780959</v>
+        <v>340.8211743104854</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33150,7 +33248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K646"/>
+  <dimension ref="A1:K648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69947,6 +70045,120 @@
         </is>
       </c>
     </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-36.71145468360649,174.7508277060256</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-36.71211594819924,174.7504371556762</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-36.71283697662251,174.75020588800214</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-36.713588410607045,174.75017533545068</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-36.7143191781682,174.75014322433123</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-36.71504508917887,174.75016885875354</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-36.7157701459799,174.750256833586</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>-36.716509034620486,174.7503020874937</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>-36.717236228211746,174.7504008472183</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-36.71145794804431,174.75083765743923</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-36.71211846691129,174.75044578480382</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-36.71283853662545,174.75021417157114</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-36.71358892536705,174.75018437981632</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-36.71431901321946,174.75014758512455</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-36.715044865672574,174.750172205447</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-36.715769405804444,174.75026348680328</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>-36.7165099910042,174.75029661792652</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>-36.7172341448159,174.75041162317115</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K648"/>
+  <dimension ref="A1:K650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25704,6 +25704,84 @@
       <c r="K648" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>334.74</v>
+      </c>
+      <c r="C649" t="n">
+        <v>330.37</v>
+      </c>
+      <c r="D649" t="n">
+        <v>336.61</v>
+      </c>
+      <c r="E649" t="n">
+        <v>347.8</v>
+      </c>
+      <c r="F649" t="n">
+        <v>344.88</v>
+      </c>
+      <c r="G649" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="H649" t="n">
+        <v>343.98</v>
+      </c>
+      <c r="I649" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="J649" t="n">
+        <v>324.91</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>334.74</v>
+      </c>
+      <c r="C650" t="n">
+        <v>330.14</v>
+      </c>
+      <c r="D650" t="n">
+        <v>336.66</v>
+      </c>
+      <c r="E650" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="F650" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="G650" t="n">
+        <v>340.01</v>
+      </c>
+      <c r="H650" t="n">
+        <v>343.56</v>
+      </c>
+      <c r="I650" t="n">
+        <v>333.32</v>
+      </c>
+      <c r="J650" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25718,7 +25796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B664"/>
+  <dimension ref="A1:B666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32361,6 +32439,26 @@
       </c>
       <c r="B664" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -32529,28 +32627,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3689841835084145</v>
+        <v>-0.3733865977920173</v>
       </c>
       <c r="J2" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K2" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3288814303209497</v>
+        <v>0.333393254112714</v>
       </c>
       <c r="M2" t="n">
-        <v>3.013348715278887</v>
+        <v>3.023665983052171</v>
       </c>
       <c r="N2" t="n">
-        <v>15.47637673249073</v>
+        <v>15.58658102728072</v>
       </c>
       <c r="O2" t="n">
-        <v>3.93400263503861</v>
+        <v>3.947984425916688</v>
       </c>
       <c r="P2" t="n">
-        <v>351.7089531184953</v>
+        <v>351.754595891464</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32611,28 +32709,28 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3945636844271005</v>
+        <v>-0.4000468194010053</v>
       </c>
       <c r="J3" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K3" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3792740685215581</v>
+        <v>0.3833474147586489</v>
       </c>
       <c r="M3" t="n">
-        <v>2.885476034868782</v>
+        <v>2.905858982805956</v>
       </c>
       <c r="N3" t="n">
-        <v>14.19302108010601</v>
+        <v>14.39428760675854</v>
       </c>
       <c r="O3" t="n">
-        <v>3.767362615956421</v>
+        <v>3.793980443644714</v>
       </c>
       <c r="P3" t="n">
-        <v>349.6665737352562</v>
+        <v>349.7234216973264</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32693,28 +32791,28 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4638527266723972</v>
+        <v>-0.4678109847588174</v>
       </c>
       <c r="J4" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K4" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3749786709014623</v>
+        <v>0.3790746907558277</v>
       </c>
       <c r="M4" t="n">
-        <v>3.518775005678276</v>
+        <v>3.533104011016997</v>
       </c>
       <c r="N4" t="n">
-        <v>19.97755748456483</v>
+        <v>20.04360880735876</v>
       </c>
       <c r="O4" t="n">
-        <v>4.469626101204085</v>
+        <v>4.477008913030971</v>
       </c>
       <c r="P4" t="n">
-        <v>355.3922348596092</v>
+        <v>355.4332725766542</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32775,28 +32873,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2296774378486987</v>
+        <v>-0.2331504760854075</v>
       </c>
       <c r="J5" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K5" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1829200907073931</v>
+        <v>0.1873432058509483</v>
       </c>
       <c r="M5" t="n">
-        <v>2.725452338816088</v>
+        <v>2.73627705404181</v>
       </c>
       <c r="N5" t="n">
-        <v>13.12603875241247</v>
+        <v>13.18446010746171</v>
       </c>
       <c r="O5" t="n">
-        <v>3.622987545163862</v>
+        <v>3.631041187794723</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0964324723908</v>
+        <v>359.1324424239151</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -32857,28 +32955,28 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1810813687863652</v>
+        <v>-0.1837230443004995</v>
       </c>
       <c r="J6" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K6" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1498108864318656</v>
+        <v>0.1537126872645254</v>
       </c>
       <c r="M6" t="n">
-        <v>2.47042461442394</v>
+        <v>2.476387221765011</v>
       </c>
       <c r="N6" t="n">
-        <v>10.3660569819136</v>
+        <v>10.39096532436558</v>
       </c>
       <c r="O6" t="n">
-        <v>3.219636156759579</v>
+        <v>3.223502027976031</v>
       </c>
       <c r="P6" t="n">
-        <v>353.8891614265057</v>
+        <v>353.9165500011335</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32939,28 +33037,28 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.214526911125019</v>
+        <v>-0.215971680468838</v>
       </c>
       <c r="J7" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K7" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1418904447520508</v>
+        <v>0.1442254661493079</v>
       </c>
       <c r="M7" t="n">
-        <v>3.038248422437315</v>
+        <v>3.037433133859871</v>
       </c>
       <c r="N7" t="n">
-        <v>15.58167249619206</v>
+        <v>15.55227578241719</v>
       </c>
       <c r="O7" t="n">
-        <v>3.947362726706536</v>
+        <v>3.943637379680996</v>
       </c>
       <c r="P7" t="n">
-        <v>348.7664267017032</v>
+        <v>348.7813545534014</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33021,28 +33119,28 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1970245080971083</v>
+        <v>-0.1969610000424773</v>
       </c>
       <c r="J8" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K8" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L8" t="n">
-        <v>0.100842677310843</v>
+        <v>0.101403334778868</v>
       </c>
       <c r="M8" t="n">
-        <v>3.365450135002445</v>
+        <v>3.3556908540972</v>
       </c>
       <c r="N8" t="n">
-        <v>19.37727695558047</v>
+        <v>19.3177247096761</v>
       </c>
       <c r="O8" t="n">
-        <v>4.401962852589794</v>
+        <v>4.395193364310164</v>
       </c>
       <c r="P8" t="n">
-        <v>348.8878399235982</v>
+        <v>348.887185074428</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33103,28 +33201,28 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2791184371327838</v>
+        <v>-0.2806073097489561</v>
       </c>
       <c r="J9" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K9" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09385892117876005</v>
+        <v>0.09531834938639649</v>
       </c>
       <c r="M9" t="n">
-        <v>5.047056967804384</v>
+        <v>5.040175850633109</v>
       </c>
       <c r="N9" t="n">
-        <v>41.89779803996286</v>
+        <v>41.78666805744486</v>
       </c>
       <c r="O9" t="n">
-        <v>6.472850843327294</v>
+        <v>6.464260828389032</v>
       </c>
       <c r="P9" t="n">
-        <v>342.9620625320785</v>
+        <v>342.977497595188</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33185,28 +33283,28 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.211438987306568</v>
+        <v>-0.217065205858906</v>
       </c>
       <c r="J10" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K10" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04419004971042317</v>
+        <v>0.0465496488851127</v>
       </c>
       <c r="M10" t="n">
-        <v>5.947838541438898</v>
+        <v>5.95958140903405</v>
       </c>
       <c r="N10" t="n">
-        <v>53.86554843315695</v>
+        <v>53.96132645369214</v>
       </c>
       <c r="O10" t="n">
-        <v>7.33931525642256</v>
+        <v>7.345837355515853</v>
       </c>
       <c r="P10" t="n">
-        <v>340.8211743104854</v>
+        <v>340.8794986843076</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33248,7 +33346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K648"/>
+  <dimension ref="A1:K650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70159,6 +70257,120 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-36.71145713193494,174.75083516958574</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-36.71211545674316,174.75043547194403</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-36.71283765399228,174.75020948481497</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-36.71358869022984,174.7501802484394</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-36.71431908512021,174.75014568426593</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-36.7150449476249,174.75017097832608</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-36.71576934412314,174.750264041238</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>-36.71650830776872,174.75030624436462</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>-36.717232566485066,174.7504197867714</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-36.71145713193494,174.75083516958574</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-36.712114750275,174.75043305157905</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-36.712837756624054,174.75021002978661</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-36.71358810556372,174.75016997582665</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-36.714319169709285,174.75014344796165</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>-36.71504599810353,174.7501552488667</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>-36.71576986224601,174.75025938398596</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>-36.716507600044466,174.75031029184416</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>-36.71722785253372,174.75044416872197</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K650"/>
+  <dimension ref="A1:K652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25780,6 +25780,84 @@
         <v>327.15</v>
       </c>
       <c r="K650" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="C651" t="n">
+        <v>328.87</v>
+      </c>
+      <c r="D651" t="n">
+        <v>335.59</v>
+      </c>
+      <c r="E651" t="n">
+        <v>346.91</v>
+      </c>
+      <c r="F651" t="n">
+        <v>344.52</v>
+      </c>
+      <c r="G651" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="H651" t="n">
+        <v>343.58</v>
+      </c>
+      <c r="I651" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="J651" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>334.35</v>
+      </c>
+      <c r="C652" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="D652" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="E652" t="n">
+        <v>347.82</v>
+      </c>
+      <c r="F652" t="n">
+        <v>346.78</v>
+      </c>
+      <c r="G652" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="H652" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="I652" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="J652" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="K652" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25796,7 +25874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B666"/>
+  <dimension ref="A1:B668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32459,6 +32537,26 @@
       </c>
       <c r="B666" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -32627,34 +32725,30 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3733865977920173</v>
+        <v>-0.3779490552921017</v>
       </c>
       <c r="J2" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K2" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L2" t="n">
-        <v>0.333393254112714</v>
+        <v>0.3379074333000703</v>
       </c>
       <c r="M2" t="n">
-        <v>3.023665983052171</v>
+        <v>3.034953732309662</v>
       </c>
       <c r="N2" t="n">
-        <v>15.58658102728072</v>
+        <v>15.70875454952551</v>
       </c>
       <c r="O2" t="n">
-        <v>3.947984425916688</v>
+        <v>3.96342712176287</v>
       </c>
       <c r="P2" t="n">
-        <v>351.754595891464</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>351.8020586224143</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.7473652854636 -36.7103188112841, 174.7569102083783 -36.71344976355121)</t>
@@ -32709,34 +32803,30 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4000468194010053</v>
+        <v>-0.4063974348792378</v>
       </c>
       <c r="J3" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K3" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3833474147586489</v>
+        <v>0.387048202917999</v>
       </c>
       <c r="M3" t="n">
-        <v>2.905858982805956</v>
+        <v>2.930641977959342</v>
       </c>
       <c r="N3" t="n">
-        <v>14.39428760675854</v>
+        <v>14.67970886396987</v>
       </c>
       <c r="O3" t="n">
-        <v>3.793980443644714</v>
+        <v>3.83141081900256</v>
       </c>
       <c r="P3" t="n">
-        <v>349.7234216973264</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>349.7894869449284</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.74695892469376 -36.71110063996396, 174.75664901036257 -36.713928887804705)</t>
@@ -32791,34 +32881,30 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4678109847588174</v>
+        <v>-0.4723617414806084</v>
       </c>
       <c r="J4" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K4" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3790746907558277</v>
+        <v>0.3832662110126868</v>
       </c>
       <c r="M4" t="n">
-        <v>3.533104011016997</v>
+        <v>3.551108280924963</v>
       </c>
       <c r="N4" t="n">
-        <v>20.04360880735876</v>
+        <v>20.151199315783</v>
       </c>
       <c r="O4" t="n">
-        <v>4.477008913030971</v>
+        <v>4.489008723068268</v>
       </c>
       <c r="P4" t="n">
-        <v>355.4332725766542</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>355.4806136743346</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.74654065739352 -36.71214665887624, 174.75657799013038 -36.714036812035616)</t>
@@ -32873,34 +32959,30 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2331504760854075</v>
+        <v>-0.2365496070382192</v>
       </c>
       <c r="J5" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K5" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1873432058509483</v>
+        <v>0.1917337040444191</v>
       </c>
       <c r="M5" t="n">
-        <v>2.73627705404181</v>
+        <v>2.746986193276153</v>
       </c>
       <c r="N5" t="n">
-        <v>13.18446010746171</v>
+        <v>13.238986154215</v>
       </c>
       <c r="O5" t="n">
-        <v>3.631041187794723</v>
+        <v>3.638541762054546</v>
       </c>
       <c r="P5" t="n">
-        <v>359.1324424239151</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>359.1678018007199</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.74629676271 -36.71336759750528, 174.75658014354633 -36.71395276593043)</t>
@@ -32955,34 +33037,30 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1837230443004995</v>
+        <v>-0.1857905160673466</v>
       </c>
       <c r="J6" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K6" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1537126872645254</v>
+        <v>0.1570559880225403</v>
       </c>
       <c r="M6" t="n">
-        <v>2.476387221765011</v>
+        <v>2.479321314060619</v>
       </c>
       <c r="N6" t="n">
-        <v>10.39096532436558</v>
+        <v>10.39789845409705</v>
       </c>
       <c r="O6" t="n">
-        <v>3.223502027976031</v>
+        <v>3.224577251997081</v>
       </c>
       <c r="P6" t="n">
-        <v>353.9165500011335</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>353.93805424151</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.74628939132742 -36.71446488825857, 174.75658717306337 -36.71407525834939)</t>
@@ -33037,34 +33115,30 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.215971680468838</v>
+        <v>-0.2173614163743932</v>
       </c>
       <c r="J7" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K7" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1442254661493079</v>
+        <v>0.1465386241504432</v>
       </c>
       <c r="M7" t="n">
-        <v>3.037433133859871</v>
+        <v>3.036288390990812</v>
       </c>
       <c r="N7" t="n">
-        <v>15.55227578241719</v>
+        <v>15.52060641502651</v>
       </c>
       <c r="O7" t="n">
-        <v>3.943637379680996</v>
+        <v>3.939620085113095</v>
       </c>
       <c r="P7" t="n">
-        <v>348.7813545534014</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>348.7957581415534</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.74636220305354 -36.71529925206989, 174.75663604418347 -36.71461300562288)</t>
@@ -33119,34 +33193,30 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1969610000424773</v>
+        <v>-0.1965284397048535</v>
       </c>
       <c r="J8" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K8" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L8" t="n">
-        <v>0.101403334778868</v>
+        <v>0.101608732179286</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3556908540972</v>
+        <v>3.347682441451211</v>
       </c>
       <c r="N8" t="n">
-        <v>19.3177247096761</v>
+        <v>19.2618197775191</v>
       </c>
       <c r="O8" t="n">
-        <v>4.395193364310164</v>
+        <v>4.388828975651603</v>
       </c>
       <c r="P8" t="n">
-        <v>348.887185074428</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>348.8826992875019</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.7464497283781 -36.71619362622589, 174.756661691286 -36.715057422673546)</t>
@@ -33201,34 +33271,30 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2806073097489561</v>
+        <v>-0.2819394567243543</v>
       </c>
       <c r="J9" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K9" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09531834938639649</v>
+        <v>0.09670421093944581</v>
       </c>
       <c r="M9" t="n">
-        <v>5.040175850633109</v>
+        <v>5.03239132401826</v>
       </c>
       <c r="N9" t="n">
-        <v>41.78666805744486</v>
+        <v>41.6725979589023</v>
       </c>
       <c r="O9" t="n">
-        <v>6.464260828389032</v>
+        <v>6.455431663250901</v>
       </c>
       <c r="P9" t="n">
-        <v>342.977497595188</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>342.9913557552084</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.7466640274627 -36.71714510889615, 174.75673780947898 -36.7153835240083)</t>
@@ -33283,34 +33349,30 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.217065205858906</v>
+        <v>-0.221209844838392</v>
       </c>
       <c r="J10" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K10" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0465496488851127</v>
+        <v>0.04845262761167091</v>
       </c>
       <c r="M10" t="n">
-        <v>5.95958140903405</v>
+        <v>5.963209591236793</v>
       </c>
       <c r="N10" t="n">
-        <v>53.96132645369214</v>
+        <v>53.93569031358005</v>
       </c>
       <c r="O10" t="n">
-        <v>7.345837355515853</v>
+        <v>7.344092204866443</v>
       </c>
       <c r="P10" t="n">
-        <v>340.8794986843076</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>340.9226148721023</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (174.7468831729906 -36.71791626878963, 174.75690673708718 -36.7159781989659)</t>
@@ -33346,7 +33408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K650"/>
+  <dimension ref="A1:K652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70371,6 +70433,120 @@
         </is>
       </c>
     </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-36.711455873766205,174.75083133414506</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-36.7121108493412,174.750419686956</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-36.712835560303546,174.7501983673937</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-36.713588124628934,174.75017031080316</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-36.71431923738053,174.7501416589182</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>-36.715045633043815,174.75016071513278</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>-36.715769837573504,174.75025960575988</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>-36.716507561789115,174.75031051062683</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>-36.717225390333944,174.750456903936</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-36.71145580575709,174.75083112682393</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-36.71210974356441,174.75041589855914</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-36.71283537556625,174.7501973864448</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-36.71358870293995,174.7501804717571</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-36.714318281521855,174.75016692915628</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>-36.71504525308344,174.75016640451167</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>-36.7157679007799,174.7502770150113</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>-36.716507561789115,174.75031051062683</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>-36.717225390333944,174.750456903936</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K652"/>
+  <dimension ref="A1:K655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25858,6 +25858,123 @@
         <v>328.32</v>
       </c>
       <c r="K652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>334.05</v>
+      </c>
+      <c r="C653" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="D653" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="E653" t="n">
+        <v>348.18</v>
+      </c>
+      <c r="F653" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="G653" t="n">
+        <v>341.58</v>
+      </c>
+      <c r="H653" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="I653" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="J653" t="n">
+        <v>330.86</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="C654" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="D654" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="E654" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="F654" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="G654" t="n">
+        <v>341.76</v>
+      </c>
+      <c r="H654" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="I654" t="n">
+        <v>336.56</v>
+      </c>
+      <c r="J654" t="n">
+        <v>329.25</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>334.32</v>
+      </c>
+      <c r="C655" t="n">
+        <v>329.61</v>
+      </c>
+      <c r="D655" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="E655" t="n">
+        <v>349.26</v>
+      </c>
+      <c r="F655" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="G655" t="n">
+        <v>340.9</v>
+      </c>
+      <c r="H655" t="n">
+        <v>344.86</v>
+      </c>
+      <c r="I655" t="n">
+        <v>331.59</v>
+      </c>
+      <c r="J655" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="K655" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25874,7 +25991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B668"/>
+  <dimension ref="A1:B671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32557,6 +32674,36 @@
       </c>
       <c r="B668" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
@@ -32725,28 +32872,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3779490552921017</v>
+        <v>-0.385153801893636</v>
       </c>
       <c r="J2" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K2" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3379074333000703</v>
+        <v>0.3446132977331757</v>
       </c>
       <c r="M2" t="n">
-        <v>3.034953732309662</v>
+        <v>3.054522858855371</v>
       </c>
       <c r="N2" t="n">
-        <v>15.70875454952551</v>
+        <v>15.92314740349686</v>
       </c>
       <c r="O2" t="n">
-        <v>3.96342712176287</v>
+        <v>3.990381861864458</v>
       </c>
       <c r="P2" t="n">
-        <v>351.8020586224143</v>
+        <v>351.8772301131293</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32803,28 +32950,28 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4063974348792378</v>
+        <v>-0.4158389782804957</v>
       </c>
       <c r="J3" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K3" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L3" t="n">
-        <v>0.387048202917999</v>
+        <v>0.3925217927241171</v>
       </c>
       <c r="M3" t="n">
-        <v>2.930641977959342</v>
+        <v>2.96780898401286</v>
       </c>
       <c r="N3" t="n">
-        <v>14.67970886396987</v>
+        <v>15.10470551640289</v>
       </c>
       <c r="O3" t="n">
-        <v>3.83141081900256</v>
+        <v>3.886477263075508</v>
       </c>
       <c r="P3" t="n">
-        <v>349.7894869449284</v>
+        <v>349.8879914962837</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32881,28 +33028,28 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4723617414806084</v>
+        <v>-0.4786207410902933</v>
       </c>
       <c r="J4" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K4" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3832662110126868</v>
+        <v>0.3893987469654037</v>
       </c>
       <c r="M4" t="n">
-        <v>3.551108280924963</v>
+        <v>3.574310130190228</v>
       </c>
       <c r="N4" t="n">
-        <v>20.151199315783</v>
+        <v>20.27407808249645</v>
       </c>
       <c r="O4" t="n">
-        <v>4.489008723068268</v>
+        <v>4.502674547699006</v>
       </c>
       <c r="P4" t="n">
-        <v>355.4806136743346</v>
+        <v>355.5459193152445</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32959,28 +33106,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2365496070382192</v>
+        <v>-0.2403173477918224</v>
       </c>
       <c r="J5" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K5" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1917337040444191</v>
+        <v>0.197352189892987</v>
       </c>
       <c r="M5" t="n">
-        <v>2.746986193276153</v>
+        <v>2.755790503650545</v>
       </c>
       <c r="N5" t="n">
-        <v>13.238986154215</v>
+        <v>13.25709179619849</v>
       </c>
       <c r="O5" t="n">
-        <v>3.638541762054546</v>
+        <v>3.641028947454069</v>
       </c>
       <c r="P5" t="n">
-        <v>359.1678018007199</v>
+        <v>359.2071082153048</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33037,28 +33184,28 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1857905160673466</v>
+        <v>-0.1867200504207449</v>
       </c>
       <c r="J6" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K6" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1570559880225403</v>
+        <v>0.1596877710733211</v>
       </c>
       <c r="M6" t="n">
-        <v>2.479321314060619</v>
+        <v>2.472627760939385</v>
       </c>
       <c r="N6" t="n">
-        <v>10.39789845409705</v>
+        <v>10.3548993097736</v>
       </c>
       <c r="O6" t="n">
-        <v>3.224577251997081</v>
+        <v>3.217902936661329</v>
       </c>
       <c r="P6" t="n">
-        <v>353.93805424151</v>
+        <v>353.9477534505031</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33115,28 +33262,28 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2173614163743932</v>
+        <v>-0.2188019979697403</v>
       </c>
       <c r="J7" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K7" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1465386241504432</v>
+        <v>0.1493916313356904</v>
       </c>
       <c r="M7" t="n">
-        <v>3.036288390990812</v>
+        <v>3.030753673209384</v>
       </c>
       <c r="N7" t="n">
-        <v>15.52060641502651</v>
+        <v>15.46150259963132</v>
       </c>
       <c r="O7" t="n">
-        <v>3.939620085113095</v>
+        <v>3.932111722679218</v>
       </c>
       <c r="P7" t="n">
-        <v>348.7957581415534</v>
+        <v>348.8107365139828</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33193,28 +33340,28 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1965284397048535</v>
+        <v>-0.1947514608096257</v>
       </c>
       <c r="J8" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K8" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="L8" t="n">
-        <v>0.101608732179286</v>
+        <v>0.1007929050362106</v>
       </c>
       <c r="M8" t="n">
-        <v>3.347682441451211</v>
+        <v>3.340766618190282</v>
       </c>
       <c r="N8" t="n">
-        <v>19.2618197775191</v>
+        <v>19.19273910665187</v>
       </c>
       <c r="O8" t="n">
-        <v>4.388828975651603</v>
+        <v>4.380951849387513</v>
       </c>
       <c r="P8" t="n">
-        <v>348.8826992875019</v>
+        <v>348.8642333530876</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33271,28 +33418,28 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2819394567243543</v>
+        <v>-0.2826974867295333</v>
       </c>
       <c r="J9" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K9" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09670421093944581</v>
+        <v>0.09802186067714469</v>
       </c>
       <c r="M9" t="n">
-        <v>5.03239132401826</v>
+        <v>5.017937637366365</v>
       </c>
       <c r="N9" t="n">
-        <v>41.6725979589023</v>
+        <v>41.5060981066919</v>
       </c>
       <c r="O9" t="n">
-        <v>6.455431663250901</v>
+        <v>6.442522650848183</v>
       </c>
       <c r="P9" t="n">
-        <v>342.9913557552084</v>
+        <v>342.9992814772169</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33349,28 +33496,28 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.221209844838392</v>
+        <v>-0.2259856675931038</v>
       </c>
       <c r="J10" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K10" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04845262761167091</v>
+        <v>0.05083789824273011</v>
       </c>
       <c r="M10" t="n">
-        <v>5.963209591236793</v>
+        <v>5.961008564646363</v>
       </c>
       <c r="N10" t="n">
-        <v>53.93569031358005</v>
+        <v>53.81576744133046</v>
       </c>
       <c r="O10" t="n">
-        <v>7.344092204866443</v>
+        <v>7.335923080385348</v>
       </c>
       <c r="P10" t="n">
-        <v>340.9226148721023</v>
+        <v>340.9724522314621</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33408,7 +33555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K652"/>
+  <dimension ref="A1:K655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70547,6 +70694,177 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-36.711454785620184,174.75082801700725</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-36.71210897566378,174.75041326772808</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-36.712837017675234,174.75020610599077</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-36.713588931722114,174.75018449147515</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-36.714317731689235,174.7501814651335</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>-36.71504482842152,174.75017276322922</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>-36.71576635874498,174.75029087587956</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>-36.7165028755035,174.75033731150268</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>-36.71722004504094,174.75048455132068</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-36.71145124914495,174.75081723631004</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-36.71210759344252,174.75040853223226</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-36.71283566293536,174.7501989123653</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-36.71358926218497,174.75019029773463</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-36.71431780782002,174.75017945245975</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>-36.715044694317676,174.75017477124527</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>-36.71576735798379,174.750281894037</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>-36.71650140266966,174.7503457346344</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>-36.71722343319984,174.7504670267978</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-36.711455703743404,174.75083081584228</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-36.712113122326436,174.75042747421654</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-36.712836525042604,174.75020349012695</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-36.713589618067715,174.75019655062945</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-36.714317803590525,174.75017956427496</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>-36.7150453350357,174.75016517739076</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>-36.71576825853178,174.75027379928977</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>-36.71651090913231,174.7502913671419</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>-36.717223538422125,174.7504664825579</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K655"/>
+  <dimension ref="A1:K657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25977,6 +25977,84 @@
       <c r="K655" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>336.88</v>
+      </c>
+      <c r="C656" t="n">
+        <v>332.48</v>
+      </c>
+      <c r="D656" t="n">
+        <v>339.31</v>
+      </c>
+      <c r="E656" t="n">
+        <v>351.37</v>
+      </c>
+      <c r="F656" t="n">
+        <v>350.08</v>
+      </c>
+      <c r="G656" t="n">
+        <v>342.62</v>
+      </c>
+      <c r="H656" t="n">
+        <v>346.08</v>
+      </c>
+      <c r="I656" t="n">
+        <v>334.01</v>
+      </c>
+      <c r="J656" t="n">
+        <v>329.56</v>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="C657" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="D657" t="n">
+        <v>339.31</v>
+      </c>
+      <c r="E657" t="n">
+        <v>349.58</v>
+      </c>
+      <c r="F657" t="n">
+        <v>348.41</v>
+      </c>
+      <c r="G657" t="n">
+        <v>342.62</v>
+      </c>
+      <c r="H657" t="n">
+        <v>344.05</v>
+      </c>
+      <c r="I657" t="n">
+        <v>334.01</v>
+      </c>
+      <c r="J657" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25991,7 +26069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B671"/>
+  <dimension ref="A1:B673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32704,6 +32782,26 @@
       </c>
       <c r="B671" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -32872,28 +32970,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.385153801893636</v>
+        <v>-0.3874135592768864</v>
       </c>
       <c r="J2" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K2" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3446132977331757</v>
+        <v>0.3481641605260449</v>
       </c>
       <c r="M2" t="n">
-        <v>3.054522858855371</v>
+        <v>3.055864402941554</v>
       </c>
       <c r="N2" t="n">
-        <v>15.92314740349686</v>
+        <v>15.91963017767678</v>
       </c>
       <c r="O2" t="n">
-        <v>3.990381861864458</v>
+        <v>3.989941124587778</v>
       </c>
       <c r="P2" t="n">
-        <v>351.8772301131293</v>
+        <v>351.9009033443521</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32950,28 +33048,28 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4158389782804957</v>
+        <v>-0.4204779405204335</v>
       </c>
       <c r="J3" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K3" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3925217927241171</v>
+        <v>0.3965496399844933</v>
       </c>
       <c r="M3" t="n">
-        <v>2.96780898401286</v>
+        <v>2.983483339224002</v>
       </c>
       <c r="N3" t="n">
-        <v>15.10470551640289</v>
+        <v>15.24261895153202</v>
       </c>
       <c r="O3" t="n">
-        <v>3.886477263075508</v>
+        <v>3.904179677157805</v>
       </c>
       <c r="P3" t="n">
-        <v>349.8879914962837</v>
+        <v>349.9365905467419</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33028,28 +33126,28 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4786207410902933</v>
+        <v>-0.4806987565042373</v>
       </c>
       <c r="J4" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K4" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3893987469654037</v>
+        <v>0.3926655271005555</v>
       </c>
       <c r="M4" t="n">
-        <v>3.574310130190228</v>
+        <v>3.576498304462146</v>
       </c>
       <c r="N4" t="n">
-        <v>20.27407808249645</v>
+        <v>20.24791570387849</v>
       </c>
       <c r="O4" t="n">
-        <v>4.502674547699006</v>
+        <v>4.499768405582502</v>
       </c>
       <c r="P4" t="n">
-        <v>355.5459193152445</v>
+        <v>355.5676889464112</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33106,28 +33204,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2403173477918224</v>
+        <v>-0.2417114734437386</v>
       </c>
       <c r="J5" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K5" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L5" t="n">
-        <v>0.197352189892987</v>
+        <v>0.200056952850615</v>
       </c>
       <c r="M5" t="n">
-        <v>2.755790503650545</v>
+        <v>2.755262243821744</v>
       </c>
       <c r="N5" t="n">
-        <v>13.25709179619849</v>
+        <v>13.23515766561094</v>
       </c>
       <c r="O5" t="n">
-        <v>3.641028947454069</v>
+        <v>3.638015621958066</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2071082153048</v>
+        <v>359.2217136395589</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33184,28 +33282,28 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1867200504207449</v>
+        <v>-0.1865436095593779</v>
       </c>
       <c r="J6" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K6" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1596877710733211</v>
+        <v>0.1603194573244887</v>
       </c>
       <c r="M6" t="n">
-        <v>2.472627760939385</v>
+        <v>2.467622406385305</v>
       </c>
       <c r="N6" t="n">
-        <v>10.3548993097736</v>
+        <v>10.32565895821862</v>
       </c>
       <c r="O6" t="n">
-        <v>3.217902936661329</v>
+        <v>3.2133563385063</v>
       </c>
       <c r="P6" t="n">
-        <v>353.9477534505031</v>
+        <v>353.9459053375904</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33262,28 +33360,28 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2188019979697403</v>
+        <v>-0.2190058126913962</v>
       </c>
       <c r="J7" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K7" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1493916313356904</v>
+        <v>0.1504935565063907</v>
       </c>
       <c r="M7" t="n">
-        <v>3.030753673209384</v>
+        <v>3.022688043450651</v>
       </c>
       <c r="N7" t="n">
-        <v>15.46150259963132</v>
+        <v>15.41471020955947</v>
       </c>
       <c r="O7" t="n">
-        <v>3.932111722679218</v>
+        <v>3.926157180954358</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8107365139828</v>
+        <v>348.8128639645709</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33340,28 +33438,28 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1947514608096257</v>
+        <v>-0.1939042860043239</v>
       </c>
       <c r="J8" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K8" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1007929050362106</v>
+        <v>0.1005764858837432</v>
       </c>
       <c r="M8" t="n">
-        <v>3.340766618190282</v>
+        <v>3.334592576565186</v>
       </c>
       <c r="N8" t="n">
-        <v>19.19273910665187</v>
+        <v>19.14334855390763</v>
       </c>
       <c r="O8" t="n">
-        <v>4.380951849387513</v>
+        <v>4.375311252231963</v>
       </c>
       <c r="P8" t="n">
-        <v>348.8642333530876</v>
+        <v>348.8553907836864</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33418,28 +33516,28 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2826974867295333</v>
+        <v>-0.2835608186607597</v>
       </c>
       <c r="J9" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K9" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09802186067714469</v>
+        <v>0.09915675427656068</v>
       </c>
       <c r="M9" t="n">
-        <v>5.017937637366365</v>
+        <v>5.007616006385325</v>
       </c>
       <c r="N9" t="n">
-        <v>41.5060981066919</v>
+        <v>41.38553145208851</v>
       </c>
       <c r="O9" t="n">
-        <v>6.442522650848183</v>
+        <v>6.433158746066236</v>
       </c>
       <c r="P9" t="n">
-        <v>342.9992814772169</v>
+        <v>343.0083258844442</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33496,28 +33594,28 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2259856675931038</v>
+        <v>-0.2293752492597158</v>
       </c>
       <c r="J10" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K10" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05083789824273011</v>
+        <v>0.0525447168026778</v>
       </c>
       <c r="M10" t="n">
-        <v>5.961008564646363</v>
+        <v>5.960541995540546</v>
       </c>
       <c r="N10" t="n">
-        <v>53.81576744133046</v>
+        <v>53.74671713093642</v>
       </c>
       <c r="O10" t="n">
-        <v>7.335923080385348</v>
+        <v>7.331215256077018</v>
       </c>
       <c r="P10" t="n">
-        <v>340.9724522314621</v>
+        <v>341.007962135215</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33555,7 +33653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K655"/>
+  <dimension ref="A1:K657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70865,6 +70963,120 @@
         </is>
       </c>
     </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-36.711464408908306,174.75085735294775</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-36.712121937818296,174.75045767616356</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-36.712843196104444,174.75023891328576</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>-36.71359095898011,174.75022011064442</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>-36.71431688578942,174.7502038281749</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>-36.71504405359888,174.75018436509959</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>-36.71576675350606,174.75028732749735</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>-36.71650628023404,174.75031783984628</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>-36.71722278082161,174.75047040108493</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-36.711470937777996,174.75087725578067</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-36.712113398770555,174.75042842131583</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-36.712843196104444,174.75023891328576</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-36.71358982142913,174.7502001237123</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>-36.71431759211605,174.75018515503538</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>-36.71504405359888,174.75018436509959</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>-36.71576925776931,174.7502648174467</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>-36.71650628023404,174.75031783984628</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>-36.7172237909556,174.75046517638222</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K657"/>
+  <dimension ref="A1:K663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26032,7 +26032,7 @@
         <v>329.7</v>
       </c>
       <c r="D657" t="n">
-        <v>339.31</v>
+        <v>336.28</v>
       </c>
       <c r="E657" t="n">
         <v>349.58</v>
@@ -26041,7 +26041,7 @@
         <v>348.41</v>
       </c>
       <c r="G657" t="n">
-        <v>342.62</v>
+        <v>340.71</v>
       </c>
       <c r="H657" t="n">
         <v>344.05</v>
@@ -26055,6 +26055,240 @@
       <c r="K657" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="C658" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="D658" t="n">
+        <v>336.43</v>
+      </c>
+      <c r="E658" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="F658" t="n">
+        <v>347.75</v>
+      </c>
+      <c r="G658" t="n">
+        <v>341.12</v>
+      </c>
+      <c r="H658" t="n">
+        <v>343.45</v>
+      </c>
+      <c r="I658" t="n">
+        <v>332.97</v>
+      </c>
+      <c r="J658" t="n">
+        <v>327.48</v>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>338.22</v>
+      </c>
+      <c r="C659" t="n">
+        <v>330.37</v>
+      </c>
+      <c r="D659" t="n">
+        <v>336.05</v>
+      </c>
+      <c r="E659" t="n">
+        <v>349.64</v>
+      </c>
+      <c r="F659" t="n">
+        <v>347.48</v>
+      </c>
+      <c r="G659" t="n">
+        <v>340.69</v>
+      </c>
+      <c r="H659" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="I659" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="J659" t="n">
+        <v>327.29</v>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>338.18</v>
+      </c>
+      <c r="C660" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="D660" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="E660" t="n">
+        <v>349.46</v>
+      </c>
+      <c r="F660" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="G660" t="n">
+        <v>340.98</v>
+      </c>
+      <c r="H660" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="I660" t="n">
+        <v>333.87</v>
+      </c>
+      <c r="J660" t="n">
+        <v>329.76</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>339</v>
+      </c>
+      <c r="C661" t="n">
+        <v>331.06</v>
+      </c>
+      <c r="D661" t="n">
+        <v>337.31</v>
+      </c>
+      <c r="E661" t="n">
+        <v>350.38</v>
+      </c>
+      <c r="F661" t="n">
+        <v>348.51</v>
+      </c>
+      <c r="G661" t="n">
+        <v>341.98</v>
+      </c>
+      <c r="H661" t="n">
+        <v>343.3</v>
+      </c>
+      <c r="I661" t="n">
+        <v>333.22</v>
+      </c>
+      <c r="J661" t="n">
+        <v>329.16</v>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>338.59</v>
+      </c>
+      <c r="C662" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="D662" t="n">
+        <v>337.3</v>
+      </c>
+      <c r="E662" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="F662" t="n">
+        <v>348.33</v>
+      </c>
+      <c r="G662" t="n">
+        <v>341.8</v>
+      </c>
+      <c r="H662" t="n">
+        <v>342.69</v>
+      </c>
+      <c r="I662" t="n">
+        <v>330.89</v>
+      </c>
+      <c r="J662" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>338.52</v>
+      </c>
+      <c r="C663" t="n">
+        <v>332.01</v>
+      </c>
+      <c r="D663" t="n">
+        <v>337.58</v>
+      </c>
+      <c r="E663" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="F663" t="n">
+        <v>348.96</v>
+      </c>
+      <c r="G663" t="n">
+        <v>342.69</v>
+      </c>
+      <c r="H663" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="I663" t="n">
+        <v>330.89</v>
+      </c>
+      <c r="J663" t="n">
+        <v>328.42</v>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B673"/>
+  <dimension ref="A1:B679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32802,6 +33036,66 @@
       </c>
       <c r="B673" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -32970,28 +33264,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3874135592768864</v>
+        <v>-0.3926407363137925</v>
       </c>
       <c r="J2" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K2" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3481641605260449</v>
+        <v>0.3577763703947325</v>
       </c>
       <c r="M2" t="n">
-        <v>3.055864402941554</v>
+        <v>3.052789217725968</v>
       </c>
       <c r="N2" t="n">
-        <v>15.91963017767678</v>
+        <v>15.85270779530532</v>
       </c>
       <c r="O2" t="n">
-        <v>3.989941124587778</v>
+        <v>3.981545905211357</v>
       </c>
       <c r="P2" t="n">
-        <v>351.9009033443521</v>
+        <v>351.9558259449603</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33048,28 +33342,28 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4204779405204335</v>
+        <v>-0.4341763087835927</v>
       </c>
       <c r="J3" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K3" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3965496399844933</v>
+        <v>0.4085117188334003</v>
       </c>
       <c r="M3" t="n">
-        <v>2.983483339224002</v>
+        <v>3.030681666096278</v>
       </c>
       <c r="N3" t="n">
-        <v>15.24261895153202</v>
+        <v>15.63550764023288</v>
       </c>
       <c r="O3" t="n">
-        <v>3.904179677157805</v>
+        <v>3.954175974869212</v>
       </c>
       <c r="P3" t="n">
-        <v>349.9365905467419</v>
+        <v>350.0805079901874</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33126,28 +33420,28 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4806987565042373</v>
+        <v>-0.4918674550493388</v>
       </c>
       <c r="J4" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K4" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3926655271005555</v>
+        <v>0.4044497985817339</v>
       </c>
       <c r="M4" t="n">
-        <v>3.576498304462146</v>
+        <v>3.613943912572993</v>
       </c>
       <c r="N4" t="n">
-        <v>20.24791570387849</v>
+        <v>20.40741729275128</v>
       </c>
       <c r="O4" t="n">
-        <v>4.499768405582502</v>
+        <v>4.517456949739674</v>
       </c>
       <c r="P4" t="n">
-        <v>355.5676889464112</v>
+        <v>355.68500062181</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33204,28 +33498,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2417114734437386</v>
+        <v>-0.2462752431206751</v>
       </c>
       <c r="J5" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K5" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="L5" t="n">
-        <v>0.200056952850615</v>
+        <v>0.2086698957836345</v>
       </c>
       <c r="M5" t="n">
-        <v>2.755262243821744</v>
+        <v>2.755865897376457</v>
       </c>
       <c r="N5" t="n">
-        <v>13.23515766561094</v>
+        <v>13.17581590963248</v>
       </c>
       <c r="O5" t="n">
-        <v>3.638015621958066</v>
+        <v>3.629850673186498</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2217136395589</v>
+        <v>359.2696579713127</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33282,28 +33576,28 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1865436095593779</v>
+        <v>-0.1879869528857732</v>
       </c>
       <c r="J6" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K6" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1603194573244887</v>
+        <v>0.1650588308562352</v>
       </c>
       <c r="M6" t="n">
-        <v>2.467622406385305</v>
+        <v>2.45267926010033</v>
       </c>
       <c r="N6" t="n">
-        <v>10.32565895821862</v>
+        <v>10.24025201046773</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2133563385063</v>
+        <v>3.200039376393317</v>
       </c>
       <c r="P6" t="n">
-        <v>353.9459053375904</v>
+        <v>353.9610596736524</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33360,28 +33654,28 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2190058126913962</v>
+        <v>-0.2220273312300606</v>
       </c>
       <c r="J7" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K7" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1504935565063907</v>
+        <v>0.1564264909281947</v>
       </c>
       <c r="M7" t="n">
-        <v>3.022688043450651</v>
+        <v>3.012476053588739</v>
       </c>
       <c r="N7" t="n">
-        <v>15.41471020955947</v>
+        <v>15.30369002170809</v>
       </c>
       <c r="O7" t="n">
-        <v>3.926157180954358</v>
+        <v>3.911993100927976</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8128639645709</v>
+        <v>348.8444651349947</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33438,28 +33732,28 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1939042860043239</v>
+        <v>-0.1947276962308235</v>
       </c>
       <c r="J8" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K8" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1005764858837432</v>
+        <v>0.1031778005936508</v>
       </c>
       <c r="M8" t="n">
-        <v>3.334592576565186</v>
+        <v>3.309679731695557</v>
       </c>
       <c r="N8" t="n">
-        <v>19.14334855390763</v>
+        <v>18.97344482505234</v>
       </c>
       <c r="O8" t="n">
-        <v>4.375311252231963</v>
+        <v>4.355851790987882</v>
       </c>
       <c r="P8" t="n">
-        <v>348.8553907836864</v>
+        <v>348.8640082272719</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33516,28 +33810,28 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2835608186607597</v>
+        <v>-0.2888902876615789</v>
       </c>
       <c r="J9" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K9" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09915675427656068</v>
+        <v>0.1041986806230196</v>
       </c>
       <c r="M9" t="n">
-        <v>5.007616006385325</v>
+        <v>4.992625764191219</v>
       </c>
       <c r="N9" t="n">
-        <v>41.38553145208851</v>
+        <v>41.10110304310938</v>
       </c>
       <c r="O9" t="n">
-        <v>6.433158746066236</v>
+        <v>6.411014197699875</v>
       </c>
       <c r="P9" t="n">
-        <v>343.0083258844442</v>
+        <v>343.0643389418549</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33594,28 +33888,28 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2293752492597158</v>
+        <v>-0.2409933941370596</v>
       </c>
       <c r="J10" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="K10" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0525447168026778</v>
+        <v>0.05839595151467025</v>
       </c>
       <c r="M10" t="n">
-        <v>5.960541995540546</v>
+        <v>5.966397695919294</v>
       </c>
       <c r="N10" t="n">
-        <v>53.74671713093642</v>
+        <v>53.64558322405411</v>
       </c>
       <c r="O10" t="n">
-        <v>7.331215256077018</v>
+        <v>7.324314522469261</v>
       </c>
       <c r="P10" t="n">
-        <v>341.007962135215</v>
+        <v>341.1300266876891</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33653,7 +33947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K657"/>
+  <dimension ref="A1:K663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71038,7 +71332,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>-36.712843196104444,174.75023891328576</t>
+          <t>-36.71283697662251,174.75020588800214</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -71053,7 +71347,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>-36.71504405359888,174.75018436509959</t>
+          <t>-36.71504547658957,174.7501630578182</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -71074,6 +71368,348 @@
       <c r="K657" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-36.71147117580963,174.75087798140484</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-36.71211536459514,174.75043515624424</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-36.71283728451787,174.75020752291707</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-36.713590151891225,174.75020592997183</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-36.714317871262296,174.7501777752316</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>-36.71504517113116,174.75016763163262</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>-36.71576999794484,174.75025816422948</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>-36.716508269513355,174.75030646314733</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>-36.71722715806724,174.7504477607055</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-36.71146896551562,174.7508712434662</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-36.71211545674316,174.75043547194403</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-36.71283650451623,174.75020338113262</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-36.7135898595594,174.7502007936653</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>-36.714317985458365,174.75017475622096</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>-36.715045491489974,174.75016283470532</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>-36.715770787465,174.75025106746423</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>-36.716509053748176,174.75030197810236</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>-36.717227557911585,174.7504456925938</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-36.71146882949751,174.75087082882385</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-36.71211524173111,174.7504347353112</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-36.71283761293957,174.75020926682632</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-36.71358974516862,174.7501987838062</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-36.71431787549178,174.75017766341642</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>-36.71504527543405,174.75016606984235</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>-36.71577061475748,174.75025261988162</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>-36.7165065480217,174.75031630836762</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>-36.71722235993239,174.75047257804434</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-36.71147161786837,174.75087932899262</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-36.71211757614734,174.7504427330391</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-36.712839090836866,174.75021711441812</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-36.71359032983223,174.75020905641932</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-36.71431754982112,174.75018627318744</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>-36.715044530412946,174.75017722548708</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>-36.71577018298867,174.7502565009251</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>-36.71650779132131,174.75030919793076</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>-36.71722362259996,174.75046604716601</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-36.71147022368303,174.75087507890817</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-36.71211892765122,174.75044736330284</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-36.71283907031053,174.7502170054238</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-36.713590418802696,174.75021061964304</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-36.71431762595198,174.75018426051372</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>-36.71504466451682,174.75017521747105</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>-36.71577093549996,174.75024973682073</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>-36.716512248068746,174.75028370974746</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>-36.71722669508954,174.75045015536116</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-36.71146998565137,174.750874353284</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-36.712120494166854,174.75045273019964</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-36.71283964504824,174.75022005726512</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-36.71359064758383,174.75021463936127</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-36.71431735949383,174.7501913048718</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>-36.71504400144732,174.7501851459947</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>-36.71576939346818,174.7502635976902</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>-36.716512248068746,174.75028370974746</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>-36.71722517988946,174.7504579924158</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0155/nzd0155.xlsx
+++ b/data/nzd0155/nzd0155.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K663"/>
+  <dimension ref="A1:K666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26281,12 +26281,129 @@
         <v>343.94</v>
       </c>
       <c r="I663" t="n">
-        <v>330.89</v>
+        <v>333.11</v>
       </c>
       <c r="J663" t="n">
         <v>328.42</v>
       </c>
       <c r="K663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="C664" t="n">
+        <v>330.69</v>
+      </c>
+      <c r="D664" t="n">
+        <v>336.93</v>
+      </c>
+      <c r="E664" t="n">
+        <v>351.21</v>
+      </c>
+      <c r="F664" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="G664" t="n">
+        <v>343.7</v>
+      </c>
+      <c r="H664" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="I664" t="n">
+        <v>337.05</v>
+      </c>
+      <c r="J664" t="n">
+        <v>329.02</v>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>335.91</v>
+      </c>
+      <c r="C665" t="n">
+        <v>330.86</v>
+      </c>
+      <c r="D665" t="n">
+        <v>337.18</v>
+      </c>
+      <c r="E665" t="n">
+        <v>351.64</v>
+      </c>
+      <c r="F665" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="G665" t="n">
+        <v>344.88</v>
+      </c>
+      <c r="H665" t="n">
+        <v>346.36</v>
+      </c>
+      <c r="I665" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="J665" t="n">
+        <v>330.11</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>335.09</v>
+      </c>
+      <c r="C666" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="D666" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="E666" t="n">
+        <v>351.8</v>
+      </c>
+      <c r="F666" t="n">
+        <v>350.46</v>
+      </c>
+      <c r="G666" t="n">
+        <v>345.06</v>
+      </c>
+      <c r="H666" t="n">
+        <v>346.64</v>
+      </c>
+      <c r="I666" t="n">
+        <v>339.98</v>
+      </c>
+      <c r="J666" t="n">
+        <v>330.16</v>
+      </c>
+      <c r="K666" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26303,7 +26420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B679"/>
+  <dimension ref="A1:B682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33096,6 +33213,36 @@
       </c>
       <c r="B679" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -33264,28 +33411,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3926407363137925</v>
+        <v>-0.3975898399720261</v>
       </c>
       <c r="J2" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K2" t="n">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3577763703947325</v>
+        <v>0.363795150154974</v>
       </c>
       <c r="M2" t="n">
-        <v>3.052789217725968</v>
+        <v>3.062325872899401</v>
       </c>
       <c r="N2" t="n">
-        <v>15.85270779530532</v>
+        <v>15.92275880460476</v>
       </c>
       <c r="O2" t="n">
-        <v>3.981545905211357</v>
+        <v>3.990333169624406</v>
       </c>
       <c r="P2" t="n">
-        <v>351.9558259449603</v>
+        <v>352.0080539950454</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33342,28 +33489,28 @@
         <v>0.0409</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4341763087835927</v>
+        <v>-0.4408765016921832</v>
       </c>
       <c r="J3" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K3" t="n">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4085117188334003</v>
+        <v>0.4143696023700434</v>
       </c>
       <c r="M3" t="n">
-        <v>3.030681666096278</v>
+        <v>3.054093970292964</v>
       </c>
       <c r="N3" t="n">
-        <v>15.63550764023288</v>
+        <v>15.82258060298597</v>
       </c>
       <c r="O3" t="n">
-        <v>3.954175974869212</v>
+        <v>3.977760752356276</v>
       </c>
       <c r="P3" t="n">
-        <v>350.0805079901874</v>
+        <v>350.1512095068269</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33420,28 +33567,28 @@
         <v>0.0409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4918674550493388</v>
+        <v>-0.4965323685598126</v>
       </c>
       <c r="J4" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K4" t="n">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4044497985817339</v>
+        <v>0.4099353401103886</v>
       </c>
       <c r="M4" t="n">
-        <v>3.613943912572993</v>
+        <v>3.626564818021865</v>
       </c>
       <c r="N4" t="n">
-        <v>20.40741729275128</v>
+        <v>20.44029056800439</v>
       </c>
       <c r="O4" t="n">
-        <v>4.517456949739674</v>
+        <v>4.521093956998061</v>
       </c>
       <c r="P4" t="n">
-        <v>355.68500062181</v>
+        <v>355.7342244008591</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33498,28 +33645,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2462752431206751</v>
+        <v>-0.2472368974645181</v>
       </c>
       <c r="J5" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K5" t="n">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2086698957836345</v>
+        <v>0.2115495741263568</v>
       </c>
       <c r="M5" t="n">
-        <v>2.755865897376457</v>
+        <v>2.748764626523615</v>
       </c>
       <c r="N5" t="n">
-        <v>13.17581590963248</v>
+        <v>13.12189315572204</v>
       </c>
       <c r="O5" t="n">
-        <v>3.629850673186498</v>
+        <v>3.622415375922817</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2696579713127</v>
+        <v>359.2798039009194</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33576,28 +33723,28 @@
         <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1879869528857732</v>
+        <v>-0.1868637492622844</v>
       </c>
       <c r="J6" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K6" t="n">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1650588308562352</v>
+        <v>0.1646800021215512</v>
       </c>
       <c r="M6" t="n">
-        <v>2.45267926010033</v>
+        <v>2.4472843548967</v>
       </c>
       <c r="N6" t="n">
-        <v>10.24025201046773</v>
+        <v>10.20163595917185</v>
       </c>
       <c r="O6" t="n">
-        <v>3.200039376393317</v>
+        <v>3.193999993608618</v>
       </c>
       <c r="P6" t="n">
-        <v>353.9610596736524</v>
+        <v>353.9492055383269</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33654,28 +33801,28 @@
         <v>0.0527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2220273312300606</v>
+        <v>-0.220556001749634</v>
       </c>
       <c r="J7" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K7" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1564264909281947</v>
+        <v>0.1558644894288784</v>
       </c>
       <c r="M7" t="n">
-        <v>3.012476053588739</v>
+        <v>3.005563537530169</v>
       </c>
       <c r="N7" t="n">
-        <v>15.30369002170809</v>
+        <v>15.24882274874009</v>
       </c>
       <c r="O7" t="n">
-        <v>3.911993100927976</v>
+        <v>3.904974103466</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8444651349947</v>
+        <v>348.8289918408269</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33732,28 +33879,28 @@
         <v>0.0469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1947276962308235</v>
+        <v>-0.1926217909971983</v>
       </c>
       <c r="J8" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K8" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1031778005936508</v>
+        <v>0.1019578222100112</v>
       </c>
       <c r="M8" t="n">
-        <v>3.309679731695557</v>
+        <v>3.304969701545801</v>
       </c>
       <c r="N8" t="n">
-        <v>18.97344482505234</v>
+        <v>18.91562013131968</v>
       </c>
       <c r="O8" t="n">
-        <v>4.355851790987882</v>
+        <v>4.34920913860436</v>
       </c>
       <c r="P8" t="n">
-        <v>348.8640082272719</v>
+        <v>348.8418621963251</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33810,28 +33957,28 @@
         <v>0.0369</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2888902876615789</v>
+        <v>-0.2851138805279991</v>
       </c>
       <c r="J9" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K9" t="n">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1041986806230196</v>
+        <v>0.1025913220434334</v>
       </c>
       <c r="M9" t="n">
-        <v>4.992625764191219</v>
+        <v>4.980253085512732</v>
       </c>
       <c r="N9" t="n">
-        <v>41.10110304310938</v>
+        <v>40.95661455874743</v>
       </c>
       <c r="O9" t="n">
-        <v>6.411014197699875</v>
+        <v>6.399735506936785</v>
       </c>
       <c r="P9" t="n">
-        <v>343.0643389418549</v>
+        <v>343.0244992330556</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33888,28 +34035,28 @@
         <v>0.0206</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2409933941370596</v>
+        <v>-0.2452922345536498</v>
       </c>
       <c r="J10" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K10" t="n">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05839595151467025</v>
+        <v>0.06082502724169236</v>
       </c>
       <c r="M10" t="n">
-        <v>5.966397695919294</v>
+        <v>5.961340094017492</v>
       </c>
       <c r="N10" t="n">
-        <v>53.64558322405411</v>
+        <v>53.51055905477838</v>
       </c>
       <c r="O10" t="n">
-        <v>7.324314522469261</v>
+        <v>7.315091185677618</v>
       </c>
       <c r="P10" t="n">
-        <v>341.1300266876891</v>
+        <v>341.1753862916643</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33947,7 +34094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K663"/>
+  <dimension ref="A1:K666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71699,7 +71846,7 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>-36.716512248068746,174.75028370974746</t>
+          <t>-36.71650800172581,174.75030799462604</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
@@ -71708,6 +71855,177 @@
         </is>
       </c>
       <c r="K663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-36.71146247064946,174.75085144429485</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-36.712116439655304,174.75043883940836</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-36.712838310835586,174.7502129726335</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-36.71359085729972,174.750218324103</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-36.71431702113368,174.7502002500883</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>-36.715043248974204,174.75019641319545</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>-36.71576799947008,174.7502761279157</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>-36.71650046541144,174.75035109480893</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>-36.717223917222334,174.75046452329437</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>-36.71146111046764,174.75084729787193</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>-36.71211696182734,174.7504406283738</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>-36.71283882399434,174.7502156974918</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>-36.71359113056573,174.7502231254331</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>-36.71431678851068,174.7502063999246</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>-36.71504236984585,174.7502095768554</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>-36.715766408090126,174.75029043233178</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>-36.71649577911682,174.75037789567952</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>-36.717221623376155,174.75047638772324</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-36.71145832209442,174.7508387977054</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-36.71211680824733,174.7504401022075</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-36.712839172942275,174.75021755039546</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>-36.713591232246046,174.75022491197456</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>-36.714316725067974,174.75020807715268</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>-36.715042235741386,174.75021158487127</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>-36.71576606267409,174.75029353716621</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>-36.71649486098493,174.7503831464619</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>-36.71722151815383,174.7504769319631</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
